--- a/nr-update-frcore-2.2.0/ig/StructureDefinition-as-dp-organization.xlsx
+++ b/nr-update-frcore-2.2.0/ig/StructureDefinition-as-dp-organization.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.0-snapshot-1</t>
+    <t>1.2.0-snapshot-2</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-18T11:49:33+00:00</t>
+    <t>2026-06-18T12:07:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -114,7 +114,7 @@
     <t>Base Definition</t>
   </si>
   <si>
-    <t>https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-organization|1.2.0-snapshot-1</t>
+    <t>https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-organization|1.2.0-snapshot-2</t>
   </si>
   <si>
     <t>Abstract</t>
@@ -397,7 +397,7 @@
     <t>as-ext-data-trace</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-data-trace|1.2.0-snapshot-1}
+    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-data-trace|1.2.0-snapshot-2}
 </t>
   </si>
   <si>
@@ -508,7 +508,7 @@
     <t>as-dp-canonical</t>
   </si>
   <si>
-    <t>https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-dp-organization|1.2.0-snapshot-1</t>
+    <t>https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-dp-organization|1.2.0-snapshot-2</t>
   </si>
   <si>
     <t>Organization.meta.security</t>
@@ -934,7 +934,7 @@
     <t>as-ext-digital-certificate</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-digital-certificate|1.2.0-snapshot-1}
+    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-digital-certificate|1.2.0-snapshot-2}
 </t>
   </si>
   <si>
@@ -950,7 +950,7 @@
     <t>as-ext-organization-pharmacy-licence</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-organization-pharmacy-licence|1.2.0-snapshot-1}
+    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-organization-pharmacy-licence|1.2.0-snapshot-2}
 </t>
   </si>
   <si>
@@ -966,7 +966,7 @@
     <t>as-ext-organization-pricing-model</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-organization-pricing-model|1.2.0-snapshot-1}
+    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-organization-pricing-model|1.2.0-snapshot-2}
 </t>
   </si>
   <si>
@@ -982,7 +982,7 @@
     <t>as-ext-organization-closing-type</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-organization-closing-type|1.2.0-snapshot-1}
+    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-organization-closing-type|1.2.0-snapshot-2}
 </t>
   </si>
   <si>
@@ -998,7 +998,7 @@
     <t>as-ext-organization-budget-type</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-organization-budget-type|1.2.0-snapshot-1}
+    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-organization-budget-type|1.2.0-snapshot-2}
 </t>
   </si>
   <si>
@@ -1014,7 +1014,7 @@
     <t>as-ext-organization-authorization-deadline</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-organization-authorization-deadline|1.2.0-snapshot-1}
+    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-organization-authorization-deadline|1.2.0-snapshot-2}
 </t>
   </si>
   <si>
@@ -1803,7 +1803,7 @@
     <t>as-ext-organization-types</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-organization-types|1.2.0-snapshot-1}
+    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-organization-types|1.2.0-snapshot-2}
 </t>
   </si>
   <si>
@@ -1843,7 +1843,7 @@
     <t>Value of extension - must be one of a constrained set of the data types (see [Extensibility](http://hl7.org/fhir/R4/extensibility.html) for a list).</t>
   </si>
   <si>
-    <t>https://interop.esante.gouv.fr/ig/fhir/annuaire/ValueSet/as-vs-organization-types|1.2.0-snapshot-1</t>
+    <t>https://interop.esante.gouv.fr/ig/fhir/annuaire/ValueSet/as-vs-organization-types|1.2.0-snapshot-2</t>
   </si>
   <si>
     <t>Organization.type:organizationType.coding</t>
@@ -2110,7 +2110,7 @@
     <t>Le type d’établissement détermine si c'est un établissement principal ou secondaire.</t>
   </si>
   <si>
-    <t>https://interop.esante.gouv.fr/ig/fhir/annuaire/ValueSet/as-vs-type-etablissement|1.2.0-snapshot-1</t>
+    <t>https://interop.esante.gouv.fr/ig/fhir/annuaire/ValueSet/as-vs-type-etablissement|1.2.0-snapshot-2</t>
   </si>
   <si>
     <t>EntiteGeographique.typeEtablissement</t>
@@ -2393,7 +2393,7 @@
     <t>mailbox-mss</t>
   </si>
   <si>
-    <t xml:space="preserve">ContactPoint {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-mailbox-mss|1.2.0-snapshot-1}
+    <t xml:space="preserve">ContactPoint {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-mailbox-mss|1.2.0-snapshot-2}
 </t>
   </si>
   <si>
@@ -2457,7 +2457,7 @@
     <t>as-mailbox-mss-metadata</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-mailbox-mss-metadata|1.2.0-snapshot-1}
+    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-mailbox-mss-metadata|1.2.0-snapshot-2}
 </t>
   </si>
   <si>
@@ -2616,7 +2616,7 @@
     <t>Organization.address</t>
   </si>
   <si>
-    <t xml:space="preserve">Address {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-address-extended|1.2.0-snapshot-1}
+    <t xml:space="preserve">Address {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-address-extended|1.2.0-snapshot-2}
 </t>
   </si>
   <si>
@@ -2658,7 +2658,7 @@
     <t>Organization.partOf</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-organization|2.2.0|https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-organization|1.2.0-snapshot-1)
+    <t xml:space="preserve">Reference(https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-organization|2.2.0|https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-organization|1.2.0-snapshot-2)
 </t>
   </si>
   <si>

--- a/nr-update-frcore-2.2.0/ig/StructureDefinition-as-dp-organization.xlsx
+++ b/nr-update-frcore-2.2.0/ig/StructureDefinition-as-dp-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-18T12:07:50+00:00</t>
+    <t>2026-06-18T13:08:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-update-frcore-2.2.0/ig/StructureDefinition-as-dp-organization.xlsx
+++ b/nr-update-frcore-2.2.0/ig/StructureDefinition-as-dp-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-18T13:08:38+00:00</t>
+    <t>2026-06-18T13:31:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
